--- a/lecture/fullstack/18회차_실습체크리스트_김윤지.xlsx
+++ b/lecture/fullstack/18회차_실습체크리스트_김윤지.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jiwab\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jiwab\Desktop\KB 부캠\KB-ITs-Your-Life\lecture\fullstack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE996E85-1B84-4AE5-941D-BA890B75741A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0A83851-1B5E-426D-B717-BAA2DB112CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6984" yWindow="1188" windowWidth="10488" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -836,7 +836,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp10.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp11.xml><?xml version="1.0" encoding="utf-8"?>
@@ -844,7 +844,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp12.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp13.xml><?xml version="1.0" encoding="utf-8"?>
@@ -860,7 +860,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp16.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp17.xml><?xml version="1.0" encoding="utf-8"?>
@@ -876,7 +876,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp20.xml><?xml version="1.0" encoding="utf-8"?>
@@ -896,7 +896,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp24.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp25.xml><?xml version="1.0" encoding="utf-8"?>
@@ -964,7 +964,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp40.xml><?xml version="1.0" encoding="utf-8"?>
@@ -976,7 +976,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp6.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
@@ -984,7 +984,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp8.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp9.xml><?xml version="1.0" encoding="utf-8"?>

--- a/lecture/fullstack/18회차_실습체크리스트_김윤지.xlsx
+++ b/lecture/fullstack/18회차_실습체크리스트_김윤지.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jiwab\Desktop\KB 부캠\KB-ITs-Your-Life\lecture\fullstack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0A83851-1B5E-426D-B717-BAA2DB112CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F5C7C8A-61CD-4D7A-942B-3D2F7DA2A687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6984" yWindow="1188" windowWidth="10488" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="12960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -631,7 +631,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -729,13 +729,41 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -813,6 +841,36 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3015,8 +3073,8 @@
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>266700</xdr:colOff>
-          <xdr:row>21</xdr:row>
-          <xdr:rowOff>7620</xdr:rowOff>
+          <xdr:row>20</xdr:row>
+          <xdr:rowOff>231738</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3082,8 +3140,8 @@
         <xdr:to>
           <xdr:col>3</xdr:col>
           <xdr:colOff>266700</xdr:colOff>
-          <xdr:row>21</xdr:row>
-          <xdr:rowOff>7620</xdr:rowOff>
+          <xdr:row>20</xdr:row>
+          <xdr:rowOff>231738</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3150,7 +3208,7 @@
           <xdr:col>2</xdr:col>
           <xdr:colOff>266700</xdr:colOff>
           <xdr:row>22</xdr:row>
-          <xdr:rowOff>7620</xdr:rowOff>
+          <xdr:rowOff>7619</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3217,7 +3275,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>266700</xdr:colOff>
           <xdr:row>22</xdr:row>
-          <xdr:rowOff>7620</xdr:rowOff>
+          <xdr:rowOff>7619</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3418,7 +3476,7 @@
           <xdr:col>2</xdr:col>
           <xdr:colOff>266700</xdr:colOff>
           <xdr:row>24</xdr:row>
-          <xdr:rowOff>7620</xdr:rowOff>
+          <xdr:rowOff>7621</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3485,7 +3543,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>266700</xdr:colOff>
           <xdr:row>24</xdr:row>
-          <xdr:rowOff>7620</xdr:rowOff>
+          <xdr:rowOff>7621</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4262,31 +4320,31 @@
         <v>62</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" ht="18" thickBot="1">
       <c r="A21" s="21"/>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="5"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="7" t="s">
+      <c r="C21" s="32"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="F21" s="35" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="21"/>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="7" t="s">
+      <c r="C22" s="27"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="F22" s="30" t="s">
         <v>64</v>
       </c>
     </row>
@@ -5063,7 +5121,7 @@
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>266700</xdr:colOff>
                     <xdr:row>21</xdr:row>
-                    <xdr:rowOff>7620</xdr:rowOff>
+                    <xdr:rowOff>0</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -5085,7 +5143,7 @@
                     <xdr:col>3</xdr:col>
                     <xdr:colOff>266700</xdr:colOff>
                     <xdr:row>21</xdr:row>
-                    <xdr:rowOff>7620</xdr:rowOff>
+                    <xdr:rowOff>0</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>

--- a/lecture/fullstack/18회차_실습체크리스트_김윤지.xlsx
+++ b/lecture/fullstack/18회차_실습체크리스트_김윤지.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jiwab\Desktop\KB 부캠\KB-ITs-Your-Life\lecture\fullstack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F5C7C8A-61CD-4D7A-942B-3D2F7DA2A687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48600E6B-4CAC-4405-A29E-4E276A104783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="12960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3588" yWindow="456" windowWidth="10488" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -800,6 +800,36 @@
     <xf numFmtId="0" fontId="17" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -842,36 +872,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -890,7 +890,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp10.xml><?xml version="1.0" encoding="utf-8"?>
@@ -898,7 +898,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp11.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp12.xml><?xml version="1.0" encoding="utf-8"?>
@@ -906,15 +906,15 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp13.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp16.xml><?xml version="1.0" encoding="utf-8"?>
@@ -922,15 +922,15 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp17.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp18.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp19.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -938,19 +938,19 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp20.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp21.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp22.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp23.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp24.xml><?xml version="1.0" encoding="utf-8"?>
@@ -958,67 +958,67 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp25.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp26.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp27.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp28.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp29.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp30.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp31.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp32.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp33.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp34.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp35.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp36.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp37.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp38.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp39.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1026,11 +1026,11 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp40.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp6.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1038,7 +1038,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp8.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1046,7 +1046,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp9.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3073,8 +3073,8 @@
         <xdr:to>
           <xdr:col>2</xdr:col>
           <xdr:colOff>266700</xdr:colOff>
-          <xdr:row>20</xdr:row>
-          <xdr:rowOff>231738</xdr:rowOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3140,8 +3140,8 @@
         <xdr:to>
           <xdr:col>3</xdr:col>
           <xdr:colOff>266700</xdr:colOff>
-          <xdr:row>20</xdr:row>
-          <xdr:rowOff>231738</xdr:rowOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3208,7 +3208,7 @@
           <xdr:col>2</xdr:col>
           <xdr:colOff>266700</xdr:colOff>
           <xdr:row>22</xdr:row>
-          <xdr:rowOff>7619</xdr:rowOff>
+          <xdr:rowOff>7620</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3275,7 +3275,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>266700</xdr:colOff>
           <xdr:row>22</xdr:row>
-          <xdr:rowOff>7619</xdr:rowOff>
+          <xdr:rowOff>7620</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3476,7 +3476,7 @@
           <xdr:col>2</xdr:col>
           <xdr:colOff>266700</xdr:colOff>
           <xdr:row>24</xdr:row>
-          <xdr:rowOff>7621</xdr:rowOff>
+          <xdr:rowOff>7620</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3543,7 +3543,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>266700</xdr:colOff>
           <xdr:row>24</xdr:row>
-          <xdr:rowOff>7621</xdr:rowOff>
+          <xdr:rowOff>7620</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4041,36 +4041,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.399999999999999">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
     </row>
     <row r="3" spans="1:6" ht="27" customHeight="1">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="32" t="s">
         <v>73</v>
       </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="20" t="s">
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="20"/>
+      <c r="F3" s="30"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
@@ -4093,7 +4093,7 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="31" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -4109,7 +4109,7 @@
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="21"/>
+      <c r="A6" s="31"/>
       <c r="B6" s="4" t="s">
         <v>6</v>
       </c>
@@ -4123,7 +4123,7 @@
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="21"/>
+      <c r="A7" s="31"/>
       <c r="B7" s="4" t="s">
         <v>7</v>
       </c>
@@ -4137,7 +4137,7 @@
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="21"/>
+      <c r="A8" s="31"/>
       <c r="B8" s="4" t="s">
         <v>8</v>
       </c>
@@ -4151,7 +4151,7 @@
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="21"/>
+      <c r="A9" s="31"/>
       <c r="B9" s="4" t="s">
         <v>9</v>
       </c>
@@ -4165,7 +4165,7 @@
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="21"/>
+      <c r="A10" s="31"/>
       <c r="B10" s="4" t="s">
         <v>10</v>
       </c>
@@ -4179,7 +4179,7 @@
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="31" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -4195,7 +4195,7 @@
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="21"/>
+      <c r="A12" s="31"/>
       <c r="B12" s="9" t="s">
         <v>69</v>
       </c>
@@ -4209,7 +4209,7 @@
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="21"/>
+      <c r="A13" s="31"/>
       <c r="B13" s="4" t="s">
         <v>13</v>
       </c>
@@ -4223,7 +4223,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="21"/>
+      <c r="A14" s="31"/>
       <c r="B14" s="4" t="s">
         <v>14</v>
       </c>
@@ -4237,7 +4237,7 @@
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="21"/>
+      <c r="A15" s="31"/>
       <c r="B15" s="4" t="s">
         <v>15</v>
       </c>
@@ -4251,7 +4251,7 @@
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="21"/>
+      <c r="A16" s="31"/>
       <c r="B16" s="4" t="s">
         <v>16</v>
       </c>
@@ -4265,7 +4265,7 @@
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="21"/>
+      <c r="A17" s="31"/>
       <c r="B17" s="4" t="s">
         <v>17</v>
       </c>
@@ -4279,7 +4279,7 @@
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="21"/>
+      <c r="A18" s="31"/>
       <c r="B18" s="4" t="s">
         <v>18</v>
       </c>
@@ -4293,7 +4293,7 @@
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="21"/>
+      <c r="A19" s="31"/>
       <c r="B19" s="4" t="s">
         <v>19</v>
       </c>
@@ -4307,7 +4307,7 @@
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="21"/>
+      <c r="A20" s="31"/>
       <c r="B20" s="4" t="s">
         <v>20</v>
       </c>
@@ -4321,35 +4321,35 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="18" thickBot="1">
-      <c r="A21" s="21"/>
-      <c r="B21" s="31" t="s">
+      <c r="A21" s="31"/>
+      <c r="B21" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="32"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="34" t="s">
+      <c r="C21" s="18"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="F21" s="35" t="s">
+      <c r="F21" s="21" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="21"/>
-      <c r="B22" s="26" t="s">
+      <c r="A22" s="31"/>
+      <c r="B22" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="27"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="29" t="s">
+      <c r="C22" s="13"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="30" t="s">
+      <c r="F22" s="16" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="21"/>
+      <c r="A23" s="31"/>
       <c r="B23" s="4" t="s">
         <v>23</v>
       </c>
@@ -4363,7 +4363,7 @@
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="21"/>
+      <c r="A24" s="31"/>
       <c r="B24" s="4" t="s">
         <v>24</v>
       </c>
@@ -4377,52 +4377,52 @@
       </c>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="15"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
+      <c r="A25" s="25"/>
+      <c r="B25" s="26"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="14" t="s">
+      <c r="A26" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="25" t="s">
+      <c r="A27" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="B27" s="25"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
-      <c r="F27" s="25"/>
+      <c r="B27" s="35"/>
+      <c r="C27" s="35"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="35"/>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" s="14" t="s">
+      <c r="A28" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
+      <c r="B28" s="24"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="A29" s="14" t="s">
+      <c r="A29" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
+      <c r="B29" s="27"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="27"/>
+      <c r="F29" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="11">
